--- a/tool/src/main/resources/xml/TableModel.xlsx
+++ b/tool/src/main/resources/xml/TableModel.xlsx
@@ -8,9 +8,12 @@
   <sheets>
     <sheet name="TableModel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -455,10 +458,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="18.875" customWidth="1" min="1" max="21"/>
+    <col min="1" max="21" customWidth="true" width="18.875" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1055,6 +1058,74 @@
       </c>
       <c r="V7" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
